--- a/2022/south3/South3_members_final.xlsx
+++ b/2022/south3/South3_members_final.xlsx
@@ -815,7 +815,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
